--- a/List of Kinetic Models.xlsx
+++ b/List of Kinetic Models.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\MyProjects\kinmodre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC26B776-21EB-404E-A452-C70B8688A1C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A9076E4-43C5-42A9-B0D3-4DAFF35A75F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A48245FD-6B6A-497E-8B16-C1CADEA3146F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="107">
   <si>
     <t>Model Name</t>
   </si>
@@ -522,6 +522,9 @@
   </si>
   <si>
     <t>Verma et al. 2026. Ab Initio Whole Cell Kinetic Model of Streptococcus thermophilus STH_CIRM_65 (stheVS26). Acta Scientific Nutritional Health 10(2): 43-47.</t>
+  </si>
+  <si>
+    <t>Cinco et al. 2026. Ab Initio Whole Cell Kinetic Model of Streptomyces murinus CR-43 (smuLA26). Journal of Clinical Immunology &amp; Microbiology 7(1): 1-5.</t>
   </si>
 </sst>
 </file>
@@ -1610,7 +1613,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>99</v>
       </c>
@@ -1631,6 +1634,9 @@
       </c>
       <c r="G26" s="2">
         <v>1009</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">

--- a/List of Kinetic Models.xlsx
+++ b/List of Kinetic Models.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\MyProjects\kinmodre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A9076E4-43C5-42A9-B0D3-4DAFF35A75F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8026F0-6DD1-4347-874F-CB2DD4483229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A48245FD-6B6A-497E-8B16-C1CADEA3146F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Models" sheetId="1" r:id="rId1"/>
+    <sheet name="Information" sheetId="2" r:id="rId1"/>
+    <sheet name="Ab Initio (ML)" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="114">
   <si>
     <t>Model Name</t>
   </si>
@@ -526,12 +527,33 @@
   <si>
     <t>Cinco et al. 2026. Ab Initio Whole Cell Kinetic Model of Streptomyces murinus CR-43 (smuLA26). Journal of Clinical Immunology &amp; Microbiology 7(1): 1-5.</t>
   </si>
+  <si>
+    <t>bceDT26</t>
+  </si>
+  <si>
+    <t>Abul-Hasan et al. 2026. Ab Initio Whole Cell Kinetic Model of Haemophilus influenzae FDAARGOS_1560 (hinSAH26). Medicon Medical Sciences 10(2): 64-68.</t>
+  </si>
+  <si>
+    <t>Srinithiksha et al. 2026. Ab Initio Whole Cell Kinetic Model of Corynebacterium glutamicum ATCC 13032 (cglPS26). Clareus Scientific Medical Sciences 3(1): 21-26.</t>
+  </si>
+  <si>
+    <t>Ab Initio (ML)</t>
+  </si>
+  <si>
+    <t>Sheet Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Ab Initio models developed by my group. For each of these models, the annotated genome of the organism was used as source to identify enzymatic genes. Each enzymatic gene was identified as a presence of complete Enzyme Commission (EC) number in the GenBank record, or via the coding sequence’s protein ID or locus tag. Each EC number is then mapped into reaction IDs via KEGG Ligand Database for Enzyme Nomenclature. From the reaction IDs, corresponding reactants and products were identified.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -565,6 +587,14 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -602,7 +632,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -623,6 +653,18 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -956,6 +998,69 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F23B4141-FBBA-428D-B844-518DC165C927}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.08984375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="106.54296875" style="9" customWidth="1"/>
+    <col min="3" max="16384" width="8.7265625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5584041-A284-4063-80B3-FA0C9EAD7AB9}">
   <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -1101,415 +1206,415 @@
     </row>
     <row r="6" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2">
         <v>2025</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E6" s="2">
-        <v>581</v>
+        <v>1369</v>
       </c>
       <c r="F6" s="2">
-        <v>580</v>
+        <v>649</v>
       </c>
       <c r="G6" s="2">
-        <v>231</v>
+        <v>1681</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="B7" s="2">
         <v>2025</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E7" s="2">
-        <v>853</v>
+        <v>1300</v>
       </c>
       <c r="F7" s="2">
-        <v>931</v>
+        <v>650</v>
       </c>
       <c r="G7" s="2">
-        <v>302</v>
+        <v>1053</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2">
         <v>2025</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>23</v>
+        <v>42</v>
+      </c>
+      <c r="D8" s="2">
+        <v>168</v>
       </c>
       <c r="E8" s="2">
-        <v>2340</v>
+        <v>1565</v>
       </c>
       <c r="F8" s="2">
-        <v>753</v>
+        <v>679</v>
       </c>
       <c r="G8" s="2">
-        <v>1624</v>
+        <v>1554</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2">
         <v>2025</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="E9" s="2">
-        <v>3012</v>
+        <v>1305</v>
       </c>
       <c r="F9" s="2">
-        <v>961</v>
+        <v>571</v>
       </c>
       <c r="G9" s="2">
-        <v>1801</v>
+        <v>1388</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B10" s="2">
         <v>2025</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E10" s="2">
-        <v>856</v>
+        <v>2340</v>
       </c>
       <c r="F10" s="2">
-        <v>703</v>
+        <v>753</v>
       </c>
       <c r="G10" s="2">
-        <v>931</v>
+        <v>1624</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2">
         <v>2025</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E11" s="2">
-        <v>1369</v>
+        <v>3012</v>
       </c>
       <c r="F11" s="2">
-        <v>649</v>
+        <v>961</v>
       </c>
       <c r="G11" s="2">
-        <v>1681</v>
+        <v>1801</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="B12" s="2">
         <v>2025</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="E12" s="2">
-        <v>1305</v>
+        <v>581</v>
       </c>
       <c r="F12" s="2">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="G12" s="2">
-        <v>1388</v>
+        <v>231</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="B13" s="2">
         <v>2025</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="E13" s="2">
-        <v>1300</v>
+        <v>853</v>
       </c>
       <c r="F13" s="2">
-        <v>650</v>
+        <v>931</v>
       </c>
       <c r="G13" s="2">
-        <v>1053</v>
+        <v>302</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B14" s="2">
         <v>2025</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="2">
-        <v>168</v>
+      <c r="C14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="E14" s="2">
-        <v>1565</v>
+        <v>9420</v>
       </c>
       <c r="F14" s="2">
-        <v>679</v>
+        <v>9420</v>
       </c>
       <c r="G14" s="2">
-        <v>1554</v>
+        <v>30669</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2">
         <v>2025</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>5</v>
+      <c r="C15" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="E15" s="2">
-        <v>9420</v>
+        <v>856</v>
       </c>
       <c r="F15" s="2">
-        <v>9420</v>
+        <v>703</v>
       </c>
       <c r="G15" s="2">
-        <v>30669</v>
+        <v>931</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B16" s="2">
         <v>2026</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="E16" s="2">
-        <v>677</v>
+        <v>1073</v>
       </c>
       <c r="F16" s="2">
-        <v>356</v>
+        <v>545</v>
       </c>
       <c r="G16" s="2">
-        <v>846</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>104</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="B17" s="2">
         <v>2026</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="E17" s="2">
-        <v>336</v>
+        <v>1182</v>
       </c>
       <c r="F17" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="G17" s="2">
-        <v>322</v>
+        <v>1097</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="B18" s="2">
         <v>2026</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>53</v>
+      <c r="C18" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="E18" s="2">
-        <v>573</v>
+        <v>1153</v>
       </c>
       <c r="F18" s="2">
-        <v>275</v>
+        <v>444</v>
       </c>
       <c r="G18" s="2">
-        <v>701</v>
+        <v>986</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="B19" s="2">
         <v>2026</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E19" s="2">
-        <v>778</v>
+        <v>573</v>
       </c>
       <c r="F19" s="2">
-        <v>364</v>
+        <v>275</v>
       </c>
       <c r="G19" s="2">
-        <v>842</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+        <v>701</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B20" s="2">
         <v>2026</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E20" s="2">
-        <v>836</v>
+        <v>699</v>
       </c>
       <c r="F20" s="2">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="G20" s="2">
-        <v>1014</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+        <v>816</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B21" s="2">
         <v>2026</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E21" s="2">
-        <v>699</v>
+        <v>677</v>
       </c>
       <c r="F21" s="2">
-        <v>452</v>
+        <v>356</v>
       </c>
       <c r="G21" s="2">
-        <v>816</v>
+        <v>846</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="31" x14ac:dyDescent="0.35">
@@ -1538,113 +1643,134 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="B23" s="2">
         <v>2026</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="E23" s="2">
-        <v>1552</v>
+        <v>1385</v>
       </c>
       <c r="F23" s="2">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="G23" s="2">
-        <v>1059</v>
+        <v>1009</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="B24" s="2">
         <v>2026</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E24" s="2">
-        <v>1182</v>
+        <v>836</v>
       </c>
       <c r="F24" s="2">
-        <v>407</v>
+        <v>460</v>
       </c>
       <c r="G24" s="2">
-        <v>1097</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1014</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="B25" s="2">
         <v>2026</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>87</v>
+      <c r="C25" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="E25" s="2">
-        <v>1153</v>
+        <v>336</v>
       </c>
       <c r="F25" s="2">
-        <v>444</v>
+        <v>400</v>
       </c>
       <c r="G25" s="2">
-        <v>986</v>
+        <v>322</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B26" s="2">
         <v>2026</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="E26" s="2">
-        <v>1385</v>
+        <v>778</v>
       </c>
       <c r="F26" s="2">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="G26" s="2">
-        <v>1009</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>106</v>
+        <v>842</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="2">
+        <v>2026</v>
+      </c>
       <c r="C27" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1552</v>
+      </c>
+      <c r="F27" s="2">
+        <v>431</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1059</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
@@ -1652,7 +1778,7 @@
         <v>68</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
@@ -1660,7 +1786,7 @@
         <v>68</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
@@ -1704,6 +1830,10 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H34">
+    <sortCondition ref="B2:B34"/>
+    <sortCondition ref="A2:A34"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/List of Kinetic Models.xlsx
+++ b/List of Kinetic Models.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\MyProjects\kinmodre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8026F0-6DD1-4347-874F-CB2DD4483229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8039EC-11AB-4A55-954B-9DA5B36CC9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A48245FD-6B6A-497E-8B16-C1CADEA3146F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A48245FD-6B6A-497E-8B16-C1CADEA3146F}"/>
   </bookViews>
   <sheets>
     <sheet name="Information" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="116">
   <si>
     <t>Model Name</t>
   </si>
@@ -547,6 +547,12 @@
   </si>
   <si>
     <t>Ab Initio models developed by my group. For each of these models, the annotated genome of the organism was used as source to identify enzymatic genes. Each enzymatic gene was identified as a presence of complete Enzyme Commission (EC) number in the GenBank record, or via the coding sequence’s protein ID or locus tag. Each EC number is then mapped into reaction IDs via KEGG Ligand Database for Enzyme Nomenclature. From the reaction IDs, corresponding reactants and products were identified.</t>
+  </si>
+  <si>
+    <t>bcgLPT26</t>
+  </si>
+  <si>
+    <t>seqSA26</t>
   </si>
 </sst>
 </file>
@@ -1790,11 +1796,26 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" s="2">
+        <v>2026</v>
+      </c>
       <c r="C30" s="3" t="s">
         <v>68</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>74</v>
+      </c>
+      <c r="E30" s="2">
+        <v>824</v>
+      </c>
+      <c r="F30" s="2">
+        <v>412</v>
+      </c>
+      <c r="G30" s="2">
+        <v>919</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
@@ -1806,11 +1827,26 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" s="2">
+        <v>2026</v>
+      </c>
       <c r="C32" s="5" t="s">
         <v>83</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>81</v>
+      </c>
+      <c r="E32" s="2">
+        <v>861</v>
+      </c>
+      <c r="F32" s="2">
+        <v>325</v>
+      </c>
+      <c r="G32" s="2">
+        <v>580</v>
       </c>
     </row>
     <row r="33" spans="3:4" x14ac:dyDescent="0.35">

--- a/List of Kinetic Models.xlsx
+++ b/List of Kinetic Models.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\MyProjects\kinmodre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8039EC-11AB-4A55-954B-9DA5B36CC9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6FDF7D-56D2-4B96-8436-09653FF24A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A48245FD-6B6A-497E-8B16-C1CADEA3146F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="117">
   <si>
     <t>Model Name</t>
   </si>
@@ -553,6 +553,9 @@
   </si>
   <si>
     <t>seqSA26</t>
+  </si>
+  <si>
+    <t>bczDT26</t>
   </si>
 </sst>
 </file>
@@ -1788,11 +1791,26 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B29" s="2">
+        <v>2026</v>
+      </c>
       <c r="C29" s="3" t="s">
         <v>68</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>67</v>
+      </c>
+      <c r="E29" s="2">
+        <v>1765</v>
+      </c>
+      <c r="F29" s="2">
+        <v>514</v>
+      </c>
+      <c r="G29" s="2">
+        <v>1230</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">

--- a/List of Kinetic Models.xlsx
+++ b/List of Kinetic Models.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\MyProjects\kinmodre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6FDF7D-56D2-4B96-8436-09653FF24A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282C4DB0-41D8-4253-AA2F-05B671438991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A48245FD-6B6A-497E-8B16-C1CADEA3146F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="119">
   <si>
     <t>Model Name</t>
   </si>
@@ -556,6 +556,12 @@
   </si>
   <si>
     <t>bczDT26</t>
+  </si>
+  <si>
+    <t>Multi-Strain</t>
+  </si>
+  <si>
+    <t>bcfKN26</t>
   </si>
 </sst>
 </file>
@@ -1071,7 +1077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5584041-A284-4063-80B3-FA0C9EAD7AB9}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.7265625" style="2" customWidth="1"/>
@@ -1189,33 +1195,33 @@
     </row>
     <row r="5" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="B5" s="2">
         <v>2025</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="E5" s="2">
-        <v>162</v>
+        <v>1369</v>
       </c>
       <c r="F5" s="2">
-        <v>236</v>
+        <v>649</v>
       </c>
       <c r="G5" s="2">
-        <v>68</v>
+        <v>1681</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B6" s="2">
         <v>2025</v>
@@ -1224,16 +1230,16 @@
         <v>42</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E6" s="2">
-        <v>1369</v>
+        <v>1300</v>
       </c>
       <c r="F6" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="G6" s="2">
-        <v>1681</v>
+        <v>1053</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>70</v>
@@ -1241,7 +1247,7 @@
     </row>
     <row r="7" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B7" s="2">
         <v>2025</v>
@@ -1249,17 +1255,17 @@
       <c r="C7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>47</v>
+      <c r="D7" s="2">
+        <v>168</v>
       </c>
       <c r="E7" s="2">
-        <v>1300</v>
+        <v>1565</v>
       </c>
       <c r="F7" s="2">
-        <v>650</v>
+        <v>679</v>
       </c>
       <c r="G7" s="2">
-        <v>1053</v>
+        <v>1554</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>70</v>
@@ -1267,7 +1273,7 @@
     </row>
     <row r="8" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B8" s="2">
         <v>2025</v>
@@ -1275,17 +1281,17 @@
       <c r="C8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="2">
-        <v>168</v>
+      <c r="D8" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="E8" s="2">
-        <v>1565</v>
+        <v>1305</v>
       </c>
       <c r="F8" s="2">
-        <v>679</v>
+        <v>571</v>
       </c>
       <c r="G8" s="2">
-        <v>1554</v>
+        <v>1388</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>70</v>
@@ -1293,28 +1299,28 @@
     </row>
     <row r="9" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="B9" s="2">
         <v>2025</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E9" s="2">
-        <v>1305</v>
+        <v>162</v>
       </c>
       <c r="F9" s="2">
-        <v>571</v>
+        <v>236</v>
       </c>
       <c r="G9" s="2">
-        <v>1388</v>
+        <v>68</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="31" x14ac:dyDescent="0.35">
@@ -1371,80 +1377,80 @@
     </row>
     <row r="12" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="B12" s="2">
         <v>2025</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>17</v>
+      <c r="C12" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E12" s="2">
-        <v>581</v>
+        <v>9420</v>
       </c>
       <c r="F12" s="2">
-        <v>580</v>
+        <v>9420</v>
       </c>
       <c r="G12" s="2">
-        <v>231</v>
+        <v>30669</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2">
         <v>2025</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E13" s="2">
-        <v>853</v>
+        <v>581</v>
       </c>
       <c r="F13" s="2">
-        <v>931</v>
+        <v>580</v>
       </c>
       <c r="G13" s="2">
-        <v>302</v>
+        <v>231</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="B14" s="2">
         <v>2025</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>5</v>
+      <c r="C14" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E14" s="2">
-        <v>9420</v>
+        <v>853</v>
       </c>
       <c r="F14" s="2">
-        <v>9420</v>
+        <v>931</v>
       </c>
       <c r="G14" s="2">
-        <v>30669</v>
+        <v>302</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -1473,398 +1479,413 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="B16" s="2">
         <v>2026</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="E16" s="2">
-        <v>1073</v>
+        <v>573</v>
       </c>
       <c r="F16" s="2">
-        <v>545</v>
+        <v>275</v>
       </c>
       <c r="G16" s="2">
-        <v>1208</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+        <v>701</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="B17" s="2">
         <v>2026</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E17" s="2">
-        <v>1182</v>
+        <v>1073</v>
       </c>
       <c r="F17" s="2">
-        <v>407</v>
+        <v>545</v>
       </c>
       <c r="G17" s="2">
-        <v>1097</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="B18" s="2">
         <v>2026</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>87</v>
+      <c r="C18" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="E18" s="2">
-        <v>1153</v>
+        <v>824</v>
       </c>
       <c r="F18" s="2">
-        <v>444</v>
+        <v>412</v>
       </c>
       <c r="G18" s="2">
-        <v>986</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="B19" s="2">
         <v>2026</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="E19" s="2">
-        <v>573</v>
+        <v>1765</v>
       </c>
       <c r="F19" s="2">
-        <v>275</v>
+        <v>514</v>
       </c>
       <c r="G19" s="2">
-        <v>701</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="B20" s="2">
         <v>2026</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E20" s="2">
-        <v>699</v>
+        <v>2418</v>
       </c>
       <c r="F20" s="2">
-        <v>452</v>
+        <v>529</v>
       </c>
       <c r="G20" s="2">
-        <v>816</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>108</v>
+        <v>802</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B21" s="2">
         <v>2026</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E21" s="2">
-        <v>677</v>
+        <v>1182</v>
       </c>
       <c r="F21" s="2">
-        <v>356</v>
+        <v>407</v>
       </c>
       <c r="G21" s="2">
-        <v>846</v>
+        <v>1097</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B22" s="2">
         <v>2026</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>61</v>
+      <c r="C22" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E22" s="2">
-        <v>752</v>
+        <v>1153</v>
       </c>
       <c r="F22" s="2">
-        <v>290</v>
+        <v>444</v>
       </c>
       <c r="G22" s="2">
-        <v>703</v>
+        <v>986</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="B23" s="2">
         <v>2026</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="E23" s="2">
-        <v>1385</v>
+        <v>699</v>
       </c>
       <c r="F23" s="2">
-        <v>424</v>
+        <v>452</v>
       </c>
       <c r="G23" s="2">
-        <v>1009</v>
+        <v>816</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="B24" s="2">
         <v>2026</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E24" s="2">
-        <v>836</v>
+        <v>677</v>
       </c>
       <c r="F24" s="2">
-        <v>460</v>
+        <v>356</v>
       </c>
       <c r="G24" s="2">
-        <v>1014</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>100</v>
+        <v>846</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="B25" s="2">
         <v>2026</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="E25" s="2">
-        <v>336</v>
+        <v>752</v>
       </c>
       <c r="F25" s="2">
-        <v>400</v>
+        <v>290</v>
       </c>
       <c r="G25" s="2">
-        <v>322</v>
+        <v>703</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="B26" s="2">
         <v>2026</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>55</v>
+      <c r="C26" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="E26" s="2">
-        <v>778</v>
+        <v>861</v>
       </c>
       <c r="F26" s="2">
-        <v>364</v>
+        <v>325</v>
       </c>
       <c r="G26" s="2">
-        <v>842</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>98</v>
+        <v>580</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B27" s="2">
         <v>2026</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E27" s="2">
-        <v>1552</v>
+        <v>836</v>
       </c>
       <c r="F27" s="2">
-        <v>431</v>
+        <v>460</v>
       </c>
       <c r="G27" s="2">
-        <v>1059</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1014</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" s="2">
+        <v>2026</v>
+      </c>
       <c r="C28" s="3" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+      <c r="E28" s="2">
+        <v>778</v>
+      </c>
+      <c r="F28" s="2">
+        <v>364</v>
+      </c>
+      <c r="G28" s="2">
+        <v>842</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="B29" s="2">
         <v>2026</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="E29" s="2">
-        <v>1765</v>
+        <v>336</v>
       </c>
       <c r="F29" s="2">
-        <v>514</v>
+        <v>400</v>
       </c>
       <c r="G29" s="2">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+        <v>322</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="B30" s="2">
         <v>2026</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="E30" s="2">
-        <v>824</v>
+        <v>1385</v>
       </c>
       <c r="F30" s="2">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="G30" s="2">
-        <v>919</v>
+        <v>1009</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C31" s="5" t="s">
+      <c r="A31" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1552</v>
+      </c>
+      <c r="F31" s="2">
+        <v>431</v>
+      </c>
+      <c r="G31" s="2">
+        <v>1059</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C32" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B32" s="2">
-        <v>2026</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E32" s="2">
-        <v>861</v>
-      </c>
-      <c r="F32" s="2">
-        <v>325</v>
-      </c>
-      <c r="G32" s="2">
-        <v>580</v>
       </c>
     </row>
     <row r="33" spans="3:4" x14ac:dyDescent="0.35">
@@ -1883,10 +1904,18 @@
         <v>86</v>
       </c>
     </row>
+    <row r="35" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C35" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H34">
-    <sortCondition ref="B2:B34"/>
-    <sortCondition ref="A2:A34"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H35">
+    <sortCondition ref="B2:B35"/>
+    <sortCondition ref="C2:C35"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/List of Kinetic Models.xlsx
+++ b/List of Kinetic Models.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\MyProjects\kinmodre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282C4DB0-41D8-4253-AA2F-05B671438991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC5BF67-BAFF-4C3A-A942-04547D563AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A48245FD-6B6A-497E-8B16-C1CADEA3146F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="120">
   <si>
     <t>Model Name</t>
   </si>
@@ -562,6 +562,9 @@
   </si>
   <si>
     <t>bcfKN26</t>
+  </si>
+  <si>
+    <t>cdlFN26</t>
   </si>
 </sst>
 </file>
@@ -1888,7 +1891,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C33" s="5" t="s">
         <v>82</v>
       </c>
@@ -1896,15 +1899,30 @@
         <v>84</v>
       </c>
     </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B34" s="2">
+        <v>2026</v>
+      </c>
       <c r="C34" s="5" t="s">
         <v>85</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="E34" s="2">
+        <v>1126</v>
+      </c>
+      <c r="F34" s="2">
+        <v>386</v>
+      </c>
+      <c r="G34" s="2">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C35" s="5" t="s">
         <v>87</v>
       </c>

--- a/List of Kinetic Models.xlsx
+++ b/List of Kinetic Models.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\MyProjects\kinmodre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC5BF67-BAFF-4C3A-A942-04547D563AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFA0D78-B532-4F9C-998E-D0A7E8371CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A48245FD-6B6A-497E-8B16-C1CADEA3146F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="121">
   <si>
     <t>Model Name</t>
   </si>
@@ -565,6 +565,9 @@
   </si>
   <si>
     <t>cdlFN26</t>
+  </si>
+  <si>
+    <t>Toh et al. 2026. Four Ab Initio Whole Cell Kinetic Models of Bacillus cereus ATCC 14579 (bceDT26), E33L (bczDT26), F837/76 (bcfKN26) and G9842 (bcgLPT26). Acta Scientific Microbiology 9(5): 33-39.</t>
   </si>
 </sst>
 </file>
@@ -1508,7 +1511,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>107</v>
       </c>
@@ -1530,8 +1533,11 @@
       <c r="G17" s="2">
         <v>1208</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H17" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>114</v>
       </c>
@@ -1553,8 +1559,11 @@
       <c r="G18" s="2">
         <v>919</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H18" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>116</v>
       </c>
@@ -1576,8 +1585,11 @@
       <c r="G19" s="2">
         <v>1230</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H19" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>118</v>
       </c>
@@ -1598,6 +1610,9 @@
       </c>
       <c r="G20" s="2">
         <v>802</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="31" x14ac:dyDescent="0.35">

--- a/List of Kinetic Models.xlsx
+++ b/List of Kinetic Models.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\MyProjects\kinmodre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFA0D78-B532-4F9C-998E-D0A7E8371CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3645B9-11DA-4797-814A-9756F6496ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A48245FD-6B6A-497E-8B16-C1CADEA3146F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="123">
   <si>
     <t>Model Name</t>
   </si>
@@ -568,6 +568,12 @@
   </si>
   <si>
     <t>Toh et al. 2026. Four Ab Initio Whole Cell Kinetic Models of Bacillus cereus ATCC 14579 (bceDT26), E33L (bczDT26), F837/76 (bcfKN26) and G9842 (bcgLPT26). Acta Scientific Microbiology 9(5): 33-39.</t>
+  </si>
+  <si>
+    <t>Ali et al. 2026. Ab Initio Whole Cell Kinetic Model of Streptococcus equi subsp. zooepidemicus SEZ13 (seqSA26). Scholastic Medical Sciences 3(6): 02-04.</t>
+  </si>
+  <si>
+    <t>blmSHM26</t>
   </si>
 </sst>
 </file>
@@ -1123,444 +1129,441 @@
     </row>
     <row r="2" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2">
-        <v>2020</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>2025</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2">
-        <v>566</v>
+        <v>162</v>
       </c>
       <c r="F2" s="2">
-        <v>306</v>
+        <v>236</v>
       </c>
       <c r="G2" s="2">
-        <v>310</v>
+        <v>68</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B3" s="2">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="E3" s="2">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="F3" s="2">
-        <v>306</v>
+        <v>275</v>
       </c>
       <c r="G3" s="2">
-        <v>310</v>
+        <v>701</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>33</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="B4" s="2">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="E4" s="2">
-        <v>802</v>
+        <v>752</v>
       </c>
       <c r="F4" s="2">
-        <v>737</v>
+        <v>290</v>
       </c>
       <c r="G4" s="2">
-        <v>533</v>
+        <v>703</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>35</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>2025</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>42</v>
+        <v>2020</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2">
-        <v>1369</v>
+        <v>566</v>
       </c>
       <c r="F5" s="2">
-        <v>649</v>
+        <v>306</v>
       </c>
       <c r="G5" s="2">
-        <v>1681</v>
+        <v>310</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2">
-        <v>1300</v>
+        <v>566</v>
       </c>
       <c r="F6" s="2">
-        <v>650</v>
+        <v>306</v>
       </c>
       <c r="G6" s="2">
-        <v>1053</v>
+        <v>310</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>115</v>
       </c>
       <c r="B7" s="2">
-        <v>2025</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="2">
-        <v>168</v>
+        <v>2026</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="E7" s="2">
-        <v>1565</v>
+        <v>861</v>
       </c>
       <c r="F7" s="2">
-        <v>679</v>
+        <v>325</v>
       </c>
       <c r="G7" s="2">
-        <v>1554</v>
+        <v>580</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="B8" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E8" s="2">
-        <v>1305</v>
+        <v>677</v>
       </c>
       <c r="F8" s="2">
-        <v>571</v>
+        <v>356</v>
       </c>
       <c r="G8" s="2">
-        <v>1388</v>
+        <v>846</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="B9" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="E9" s="2">
-        <v>162</v>
+        <v>778</v>
       </c>
       <c r="F9" s="2">
-        <v>236</v>
+        <v>364</v>
       </c>
       <c r="G9" s="2">
-        <v>68</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+        <v>842</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>22</v>
+        <v>119</v>
       </c>
       <c r="B10" s="2">
-        <v>2025</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>8</v>
+        <v>2026</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="E10" s="2">
-        <v>2340</v>
+        <v>1126</v>
       </c>
       <c r="F10" s="2">
-        <v>753</v>
+        <v>386</v>
       </c>
       <c r="G10" s="2">
-        <v>1624</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>39</v>
+        <v>880</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="B11" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="E11" s="2">
-        <v>3012</v>
+        <v>336</v>
       </c>
       <c r="F11" s="2">
-        <v>961</v>
+        <v>400</v>
       </c>
       <c r="G11" s="2">
-        <v>1801</v>
+        <v>322</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>39</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="B12" s="2">
-        <v>2025</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>5</v>
+        <v>2026</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="E12" s="2">
-        <v>9420</v>
+        <v>1182</v>
       </c>
       <c r="F12" s="2">
-        <v>9420</v>
+        <v>407</v>
       </c>
       <c r="G12" s="2">
-        <v>30669</v>
+        <v>1097</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>16</v>
+        <v>114</v>
       </c>
       <c r="B13" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="E13" s="2">
-        <v>581</v>
+        <v>824</v>
       </c>
       <c r="F13" s="2">
-        <v>580</v>
+        <v>412</v>
       </c>
       <c r="G13" s="2">
-        <v>231</v>
+        <v>919</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>37</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="B14" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="E14" s="2">
-        <v>853</v>
+        <v>1385</v>
       </c>
       <c r="F14" s="2">
-        <v>931</v>
+        <v>424</v>
       </c>
       <c r="G14" s="2">
-        <v>302</v>
+        <v>1009</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>38</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="B15" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="E15" s="2">
-        <v>856</v>
+        <v>1552</v>
       </c>
       <c r="F15" s="2">
-        <v>703</v>
+        <v>431</v>
       </c>
       <c r="G15" s="2">
-        <v>931</v>
+        <v>1059</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="B16" s="2">
         <v>2026</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>53</v>
+      <c r="C16" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="E16" s="2">
-        <v>573</v>
+        <v>1153</v>
       </c>
       <c r="F16" s="2">
-        <v>275</v>
+        <v>444</v>
       </c>
       <c r="G16" s="2">
-        <v>701</v>
+        <v>986</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="B17" s="2">
         <v>2026</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E17" s="2">
-        <v>1073</v>
+        <v>699</v>
       </c>
       <c r="F17" s="2">
-        <v>545</v>
+        <v>452</v>
       </c>
       <c r="G17" s="2">
-        <v>1208</v>
+        <v>816</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="B18" s="2">
         <v>2026</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E18" s="2">
-        <v>824</v>
+        <v>836</v>
       </c>
       <c r="F18" s="2">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="G18" s="2">
-        <v>919</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>120</v>
+        <v>1014</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="31" x14ac:dyDescent="0.35">
@@ -1617,324 +1620,345 @@
     </row>
     <row r="21" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="B21" s="2">
         <v>2026</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E21" s="2">
-        <v>1182</v>
+        <v>1073</v>
       </c>
       <c r="F21" s="2">
-        <v>407</v>
+        <v>545</v>
       </c>
       <c r="G21" s="2">
-        <v>1097</v>
+        <v>1208</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="B22" s="2">
-        <v>2026</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>87</v>
+        <v>2025</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="E22" s="2">
-        <v>1153</v>
+        <v>1305</v>
       </c>
       <c r="F22" s="2">
-        <v>444</v>
+        <v>571</v>
       </c>
       <c r="G22" s="2">
-        <v>986</v>
+        <v>1388</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>109</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="B23" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="E23" s="2">
-        <v>699</v>
+        <v>581</v>
       </c>
       <c r="F23" s="2">
-        <v>452</v>
+        <v>580</v>
       </c>
       <c r="G23" s="2">
-        <v>816</v>
+        <v>231</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>108</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="B24" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E24" s="2">
-        <v>677</v>
+        <v>1369</v>
       </c>
       <c r="F24" s="2">
-        <v>356</v>
+        <v>649</v>
       </c>
       <c r="G24" s="2">
-        <v>846</v>
+        <v>1681</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="B25" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="E25" s="2">
-        <v>752</v>
+        <v>1300</v>
       </c>
       <c r="F25" s="2">
-        <v>290</v>
+        <v>650</v>
       </c>
       <c r="G25" s="2">
-        <v>703</v>
+        <v>1053</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="B26" s="2">
-        <v>2026</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>81</v>
+        <v>2025</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" s="2">
+        <v>168</v>
       </c>
       <c r="E26" s="2">
-        <v>861</v>
+        <v>1565</v>
       </c>
       <c r="F26" s="2">
-        <v>325</v>
+        <v>679</v>
       </c>
       <c r="G26" s="2">
-        <v>580</v>
+        <v>1554</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="E27" s="2">
-        <v>836</v>
+        <v>856</v>
       </c>
       <c r="F27" s="2">
-        <v>460</v>
+        <v>703</v>
       </c>
       <c r="G27" s="2">
-        <v>1014</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>100</v>
+        <v>931</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="B28" s="2">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="E28" s="2">
-        <v>778</v>
+        <v>802</v>
       </c>
       <c r="F28" s="2">
-        <v>364</v>
+        <v>737</v>
       </c>
       <c r="G28" s="2">
-        <v>842</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>98</v>
+        <v>533</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="B29" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="E29" s="2">
-        <v>336</v>
+        <v>2340</v>
       </c>
       <c r="F29" s="2">
-        <v>400</v>
+        <v>753</v>
       </c>
       <c r="G29" s="2">
-        <v>322</v>
+        <v>1624</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>105</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="B30" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="E30" s="2">
-        <v>1385</v>
+        <v>853</v>
       </c>
       <c r="F30" s="2">
-        <v>424</v>
+        <v>931</v>
       </c>
       <c r="G30" s="2">
-        <v>1009</v>
+        <v>302</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="B31" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="E31" s="2">
-        <v>1552</v>
+        <v>3012</v>
       </c>
       <c r="F31" s="2">
-        <v>431</v>
+        <v>961</v>
       </c>
       <c r="G31" s="2">
-        <v>1059</v>
+        <v>1801</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C32" s="5" t="s">
-        <v>79</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B32" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>80</v>
+        <v>6</v>
+      </c>
+      <c r="E32" s="2">
+        <v>9420</v>
+      </c>
+      <c r="F32" s="2">
+        <v>9420</v>
+      </c>
+      <c r="G32" s="2">
+        <v>30669</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C33" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B34" s="2">
         <v>2026</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E34" s="2">
-        <v>1126</v>
+        <v>753</v>
       </c>
       <c r="F34" s="2">
-        <v>386</v>
+        <v>326</v>
       </c>
       <c r="G34" s="2">
-        <v>880</v>
+        <v>731</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
@@ -1947,8 +1971,7 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H35">
-    <sortCondition ref="B2:B35"/>
-    <sortCondition ref="C2:C35"/>
+    <sortCondition ref="F2:F35"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/List of Kinetic Models.xlsx
+++ b/List of Kinetic Models.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\MyProjects\kinmodre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3645B9-11DA-4797-814A-9756F6496ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD4531A-2DC5-463C-A8AD-1AF6B26A0E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A48245FD-6B6A-497E-8B16-C1CADEA3146F}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Information" sheetId="2" r:id="rId1"/>
     <sheet name="Ab Initio (ML)" sheetId="1" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Ab Initio (ML)'!$A$1:$H$35</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="124">
   <si>
     <t>Model Name</t>
   </si>
@@ -574,6 +577,9 @@
   </si>
   <si>
     <t>blmSHM26</t>
+  </si>
+  <si>
+    <t>cglTY26</t>
   </si>
 </sst>
 </file>
@@ -1089,6 +1095,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5584041-A284-4063-80B3-FA0C9EAD7AB9}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1127,7 +1134,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
@@ -1153,7 +1160,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>72</v>
       </c>
@@ -1179,7 +1186,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>90</v>
       </c>
@@ -1205,7 +1212,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1231,7 +1238,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -1257,7 +1264,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>115</v>
       </c>
@@ -1283,7 +1290,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>89</v>
       </c>
@@ -1309,7 +1316,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>95</v>
       </c>
@@ -1335,7 +1342,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>119</v>
       </c>
@@ -1358,7 +1365,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>77</v>
       </c>
@@ -1384,7 +1391,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>91</v>
       </c>
@@ -1410,7 +1417,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>114</v>
       </c>
@@ -1436,7 +1443,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>99</v>
       </c>
@@ -1462,7 +1469,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>73</v>
       </c>
@@ -1514,7 +1521,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>78</v>
       </c>
@@ -1540,7 +1547,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>76</v>
       </c>
@@ -1566,7 +1573,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>116</v>
       </c>
@@ -1592,7 +1599,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>118</v>
       </c>
@@ -1618,7 +1625,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>107</v>
       </c>
@@ -1644,7 +1651,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>44</v>
       </c>
@@ -1670,7 +1677,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>16</v>
       </c>
@@ -1696,7 +1703,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>41</v>
       </c>
@@ -1722,7 +1729,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>46</v>
       </c>
@@ -1748,7 +1755,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>48</v>
       </c>
@@ -1774,7 +1781,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>26</v>
       </c>
@@ -1800,7 +1807,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>10</v>
       </c>
@@ -1826,7 +1833,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>22</v>
       </c>
@@ -1852,7 +1859,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>19</v>
       </c>
@@ -1878,7 +1885,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>24</v>
       </c>
@@ -1904,7 +1911,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>69</v>
       </c>
@@ -1930,7 +1937,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="C33" s="5" t="s">
         <v>79</v>
       </c>
@@ -1938,7 +1945,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>122</v>
       </c>
@@ -1962,14 +1969,36 @@
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B35" s="2">
+        <v>2026</v>
+      </c>
       <c r="C35" s="5" t="s">
         <v>87</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>117</v>
       </c>
+      <c r="E35" s="2">
+        <v>1195</v>
+      </c>
+      <c r="F35" s="2">
+        <v>511</v>
+      </c>
+      <c r="G35" s="2">
+        <v>1109</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H35" xr:uid="{E5584041-A284-4063-80B3-FA0C9EAD7AB9}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Corynebacterium glutamicum"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H35">
     <sortCondition ref="F2:F35"/>
   </sortState>

--- a/List of Kinetic Models.xlsx
+++ b/List of Kinetic Models.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\MyProjects\kinmodre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD4531A-2DC5-463C-A8AD-1AF6B26A0E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C4DC76-D14F-47F5-A13F-FAE56F5DD5FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A48245FD-6B6A-497E-8B16-C1CADEA3146F}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="127">
   <si>
     <t>Model Name</t>
   </si>
@@ -580,6 +580,15 @@
   </si>
   <si>
     <t>cglTY26</t>
+  </si>
+  <si>
+    <t>ATCC 12472</t>
+  </si>
+  <si>
+    <t>Chromobacterium violaceum</t>
+  </si>
+  <si>
+    <t>cviFA26</t>
   </si>
 </sst>
 </file>
@@ -1095,8 +1104,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5584041-A284-4063-80B3-FA0C9EAD7AB9}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.7265625" style="2" customWidth="1"/>
@@ -1134,7 +1142,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
@@ -1160,7 +1168,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>72</v>
       </c>
@@ -1186,7 +1194,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>90</v>
       </c>
@@ -1212,7 +1220,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1238,7 +1246,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -1264,7 +1272,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>115</v>
       </c>
@@ -1290,7 +1298,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>89</v>
       </c>
@@ -1316,7 +1324,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>95</v>
       </c>
@@ -1342,7 +1350,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>119</v>
       </c>
@@ -1365,7 +1373,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>77</v>
       </c>
@@ -1391,7 +1399,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>91</v>
       </c>
@@ -1417,7 +1425,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>114</v>
       </c>
@@ -1443,7 +1451,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>99</v>
       </c>
@@ -1469,7 +1477,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>73</v>
       </c>
@@ -1521,7 +1529,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>78</v>
       </c>
@@ -1547,7 +1555,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>76</v>
       </c>
@@ -1573,7 +1581,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>116</v>
       </c>
@@ -1599,7 +1607,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>118</v>
       </c>
@@ -1625,7 +1633,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>107</v>
       </c>
@@ -1651,7 +1659,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>44</v>
       </c>
@@ -1677,7 +1685,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>16</v>
       </c>
@@ -1703,7 +1711,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>41</v>
       </c>
@@ -1729,7 +1737,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>46</v>
       </c>
@@ -1755,7 +1763,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>48</v>
       </c>
@@ -1781,7 +1789,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>26</v>
       </c>
@@ -1807,7 +1815,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>10</v>
       </c>
@@ -1833,7 +1841,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>22</v>
       </c>
@@ -1859,7 +1867,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>19</v>
       </c>
@@ -1885,7 +1893,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>24</v>
       </c>
@@ -1911,7 +1919,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>69</v>
       </c>
@@ -1937,7 +1945,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C33" s="5" t="s">
         <v>79</v>
       </c>
@@ -1945,7 +1953,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>122</v>
       </c>
@@ -1991,14 +1999,31 @@
         <v>1109</v>
       </c>
     </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B36" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E36" s="2">
+        <v>1736</v>
+      </c>
+      <c r="F36" s="2">
+        <v>618</v>
+      </c>
+      <c r="G36" s="2">
+        <v>1255</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H35" xr:uid="{E5584041-A284-4063-80B3-FA0C9EAD7AB9}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Corynebacterium glutamicum"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:H35" xr:uid="{E5584041-A284-4063-80B3-FA0C9EAD7AB9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H35">
     <sortCondition ref="F2:F35"/>
   </sortState>

--- a/List of Kinetic Models.xlsx
+++ b/List of Kinetic Models.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\MyProjects\kinmodre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C4DC76-D14F-47F5-A13F-FAE56F5DD5FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0227471-8000-4529-AE4F-4D7D49DA1882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A48245FD-6B6A-497E-8B16-C1CADEA3146F}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="128">
   <si>
     <t>Model Name</t>
   </si>
@@ -589,6 +589,9 @@
   </si>
   <si>
     <t>cviFA26</t>
+  </si>
+  <si>
+    <t>bbrdPS26</t>
   </si>
 </sst>
 </file>
@@ -1946,11 +1949,26 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B33" s="2">
+        <v>2026</v>
+      </c>
       <c r="C33" s="5" t="s">
         <v>79</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>80</v>
+      </c>
+      <c r="E33" s="2">
+        <v>580</v>
+      </c>
+      <c r="F33" s="2">
+        <v>329</v>
+      </c>
+      <c r="G33" s="2">
+        <v>453</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">

--- a/List of Kinetic Models.xlsx
+++ b/List of Kinetic Models.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\MyProjects\kinmodre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0227471-8000-4529-AE4F-4D7D49DA1882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983BD7FF-7989-4A58-90E3-C6FFDF1D3E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A48245FD-6B6A-497E-8B16-C1CADEA3146F}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="129">
   <si>
     <t>Model Name</t>
   </si>
@@ -435,9 +435,6 @@
     <t>G9842</t>
   </si>
   <si>
-    <t>Ambel et al. 2025. UniKin2 – A Universal, Pan-Reactome Kinetic Model. International Journal of Research in Medical and Clinical Science 3(2): 77-80.</t>
-  </si>
-  <si>
     <t>spnLHP26</t>
   </si>
   <si>
@@ -592,6 +589,12 @@
   </si>
   <si>
     <t>bbrdPS26</t>
+  </si>
+  <si>
+    <t>Ambel et al. (2025) UniKin2 – A Universal, Pan-Reactome Kinetic Model. International Journal of Research in Medical and Clinical Science 3(2): 77-80.</t>
+  </si>
+  <si>
+    <t>Modankap et al. (2026) Ab Initio Whole Cell Kinetic Model of Bifidobacterium longum subsp. longum JCM1217 (blmSHM26). American Journal of Pathology &amp; Research 5(8): 1-5.</t>
   </si>
 </sst>
 </file>
@@ -1054,18 +1057,18 @@
   <sheetData>
     <row r="1" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>111</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1194,12 +1197,12 @@
         <v>701</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B4" s="2">
         <v>2026</v>
@@ -1208,7 +1211,7 @@
         <v>61</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E4" s="2">
         <v>752</v>
@@ -1220,7 +1223,7 @@
         <v>703</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="31" x14ac:dyDescent="0.35">
@@ -1277,16 +1280,16 @@
     </row>
     <row r="7" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B7" s="2">
         <v>2026</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E7" s="2">
         <v>861</v>
@@ -1298,12 +1301,12 @@
         <v>580</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B8" s="2">
         <v>2026</v>
@@ -1324,12 +1327,12 @@
         <v>846</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B9" s="2">
         <v>2026</v>
@@ -1350,21 +1353,21 @@
         <v>842</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B10" s="2">
         <v>2026</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="E10" s="2">
         <v>1126</v>
@@ -1378,7 +1381,7 @@
     </row>
     <row r="11" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B11" s="2">
         <v>2026</v>
@@ -1399,12 +1402,12 @@
         <v>322</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B12" s="2">
         <v>2026</v>
@@ -1425,12 +1428,12 @@
         <v>1097</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B13" s="2">
         <v>2026</v>
@@ -1451,21 +1454,21 @@
         <v>919</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B14" s="2">
         <v>2026</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E14" s="2">
         <v>1385</v>
@@ -1477,7 +1480,7 @@
         <v>1009</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -1503,21 +1506,21 @@
         <v>1059</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B16" s="2">
         <v>2026</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="E16" s="2">
         <v>1153</v>
@@ -1529,12 +1532,12 @@
         <v>986</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B17" s="2">
         <v>2026</v>
@@ -1555,12 +1558,12 @@
         <v>816</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B18" s="2">
         <v>2026</v>
@@ -1581,12 +1584,12 @@
         <v>1014</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B19" s="2">
         <v>2026</v>
@@ -1607,12 +1610,12 @@
         <v>1230</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B20" s="2">
         <v>2026</v>
@@ -1633,12 +1636,12 @@
         <v>802</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B21" s="2">
         <v>2026</v>
@@ -1659,7 +1662,7 @@
         <v>1208</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="31" x14ac:dyDescent="0.35">
@@ -1945,21 +1948,21 @@
         <v>30669</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B33" s="2">
         <v>2026</v>
       </c>
       <c r="C33" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="E33" s="2">
         <v>580</v>
@@ -1971,18 +1974,18 @@
         <v>453</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" ht="31" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B34" s="2">
         <v>2026</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E34" s="2">
         <v>753</v>
@@ -1993,19 +1996,22 @@
       <c r="G34" s="2">
         <v>731</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H34" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B35" s="2">
         <v>2026</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E35" s="2">
         <v>1195</v>
@@ -2017,18 +2023,18 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B36" s="2">
         <v>2026</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E36" s="2">
         <v>1736</v>
